--- a/Selecionados_Motivacional_Ribaue_2026.xlsx
+++ b/Selecionados_Motivacional_Ribaue_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://muvamozorg.sharepoint.com/sites/mis.drive/Documentos Partilhados/PROJECTOS/Sistema de Monitoria/Abrindo_Oportunidades/2026/Dash_Abrindo_2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="89" documentId="11_F833A363A5E9B997DDF5DE690BDD84802C57B85D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BD9A7FD1-EA6E-401A-B767-E4EAB241655B}"/>
+  <xr:revisionPtr revIDLastSave="94" documentId="11_F833A363A5E9B997DDF5DE690BDD84802C57B85D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AD200B81-A4DB-49B1-9DD1-30C90856181F}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33450" yWindow="2805" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23129" uniqueCount="5596">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23169" uniqueCount="5603">
   <si>
     <t>interview__key</t>
   </si>
@@ -16693,9 +16693,6 @@
     <t>157e089f4d16461c8a3042ca4df97e3b</t>
   </si>
   <si>
-    <t>ATIJA ANSELMO RUA</t>
-  </si>
-  <si>
     <t>2124408</t>
   </si>
   <si>
@@ -16808,6 +16805,30 @@
   </si>
   <si>
     <t>TELMA JOSE LAMPIAO</t>
+  </si>
+  <si>
+    <t>84-75-64-37</t>
+  </si>
+  <si>
+    <t>c215a35128e64b2f863ea74d5b4e68eb</t>
+  </si>
+  <si>
+    <t>ESTEFANIA FELIZARDO</t>
+  </si>
+  <si>
+    <t>AO_2026_0663</t>
+  </si>
+  <si>
+    <t>2026-07-13T12:25:04</t>
+  </si>
+  <si>
+    <t>032107720050S</t>
+  </si>
+  <si>
+    <t>876-140-379</t>
+  </si>
+  <si>
+    <t>ATIJA  ANSELMO RUA</t>
   </si>
 </sst>
 </file>
@@ -16900,8 +16921,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0E9F7243-0B27-4568-942D-7201B3F0C08F}" name="Table1" displayName="Table1" ref="A1:AX663" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="A1:AX663" xr:uid="{0E9F7243-0B27-4568-942D-7201B3F0C08F}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0E9F7243-0B27-4568-942D-7201B3F0C08F}" name="Table1" displayName="Table1" ref="A1:AX664" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A1:AX664" xr:uid="{0E9F7243-0B27-4568-942D-7201B3F0C08F}"/>
   <tableColumns count="50">
     <tableColumn id="1" xr3:uid="{9FC13388-9F59-463F-9535-1E06DD20884E}" name="interview__key"/>
     <tableColumn id="2" xr3:uid="{AB23A961-9E83-4AB5-B367-21C1014FF006}" name="interview__id"/>
@@ -17245,7 +17266,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AX663"/>
+  <dimension ref="A1:AX664"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.28515625" customWidth="1"/>
@@ -101892,7 +101913,7 @@
         <v>56</v>
       </c>
       <c r="J647" t="s">
-        <v>5578</v>
+        <v>5577</v>
       </c>
       <c r="K647" t="s">
         <v>5493</v>
@@ -102011,7 +102032,7 @@
         <v>56</v>
       </c>
       <c r="J648" t="s">
-        <v>5579</v>
+        <v>5578</v>
       </c>
       <c r="K648" t="s">
         <v>5496</v>
@@ -102130,7 +102151,7 @@
         <v>56</v>
       </c>
       <c r="J649" t="s">
-        <v>5580</v>
+        <v>5579</v>
       </c>
       <c r="K649" t="s">
         <v>5503</v>
@@ -102255,7 +102276,7 @@
         <v>56</v>
       </c>
       <c r="J650" t="s">
-        <v>5581</v>
+        <v>5580</v>
       </c>
       <c r="K650" t="s">
         <v>5510</v>
@@ -102371,7 +102392,7 @@
         <v>56</v>
       </c>
       <c r="J651" t="s">
-        <v>5582</v>
+        <v>5581</v>
       </c>
       <c r="K651" t="s">
         <v>5516</v>
@@ -102496,7 +102517,7 @@
         <v>56</v>
       </c>
       <c r="J652" t="s">
-        <v>5583</v>
+        <v>5582</v>
       </c>
       <c r="K652" t="s">
         <v>5517</v>
@@ -102633,7 +102654,7 @@
         <v>56</v>
       </c>
       <c r="J653" t="s">
-        <v>5584</v>
+        <v>5583</v>
       </c>
       <c r="K653" t="s">
         <v>5520</v>
@@ -102767,7 +102788,7 @@
         <v>56</v>
       </c>
       <c r="J654" t="s">
-        <v>5585</v>
+        <v>5584</v>
       </c>
       <c r="K654" t="s">
         <v>5530</v>
@@ -102901,7 +102922,7 @@
         <v>56</v>
       </c>
       <c r="J655" t="s">
-        <v>5586</v>
+        <v>5585</v>
       </c>
       <c r="K655" t="s">
         <v>5535</v>
@@ -103023,10 +103044,10 @@
         <v>56</v>
       </c>
       <c r="J656" t="s">
-        <v>5587</v>
+        <v>5586</v>
       </c>
       <c r="K656" t="s">
-        <v>5595</v>
+        <v>5594</v>
       </c>
       <c r="L656" t="s">
         <v>57</v>
@@ -103157,7 +103178,7 @@
         <v>56</v>
       </c>
       <c r="J657" t="s">
-        <v>5588</v>
+        <v>5587</v>
       </c>
       <c r="K657" t="s">
         <v>5541</v>
@@ -103175,7 +103196,7 @@
         <v>79</v>
       </c>
       <c r="T657" t="s">
-        <v>5558</v>
+        <v>5557</v>
       </c>
       <c r="U657" t="s">
         <v>61</v>
@@ -103196,7 +103217,7 @@
         <v>56</v>
       </c>
       <c r="AA657" t="s">
-        <v>5559</v>
+        <v>5558</v>
       </c>
       <c r="AB657" t="s">
         <v>56</v>
@@ -103294,7 +103315,7 @@
         <v>56</v>
       </c>
       <c r="J658" t="s">
-        <v>5589</v>
+        <v>5588</v>
       </c>
       <c r="K658" t="s">
         <v>5542</v>
@@ -103440,13 +103461,13 @@
         <v>56</v>
       </c>
       <c r="J659" t="s">
-        <v>5590</v>
+        <v>5589</v>
       </c>
       <c r="K659" t="s">
         <v>5545</v>
       </c>
       <c r="L659" t="s">
-        <v>5560</v>
+        <v>5559</v>
       </c>
       <c r="Q659" t="s">
         <v>57</v>
@@ -103458,7 +103479,7 @@
         <v>59</v>
       </c>
       <c r="T659" t="s">
-        <v>5561</v>
+        <v>5560</v>
       </c>
       <c r="U659" t="s">
         <v>61</v>
@@ -103479,7 +103500,7 @@
         <v>56</v>
       </c>
       <c r="AA659" t="s">
-        <v>5562</v>
+        <v>5561</v>
       </c>
       <c r="AB659" t="s">
         <v>56</v>
@@ -103577,7 +103598,7 @@
         <v>56</v>
       </c>
       <c r="J660" t="s">
-        <v>5591</v>
+        <v>5590</v>
       </c>
       <c r="K660" t="s">
         <v>5548</v>
@@ -103595,7 +103616,7 @@
         <v>79</v>
       </c>
       <c r="T660" t="s">
-        <v>5563</v>
+        <v>5562</v>
       </c>
       <c r="U660" t="s">
         <v>61</v>
@@ -103714,13 +103735,13 @@
         <v>56</v>
       </c>
       <c r="J661" t="s">
-        <v>5592</v>
+        <v>5591</v>
       </c>
       <c r="K661" t="s">
         <v>5551</v>
       </c>
       <c r="L661" t="s">
-        <v>5564</v>
+        <v>5563</v>
       </c>
       <c r="M661">
         <v>-14.944319399999999</v>
@@ -103732,7 +103753,7 @@
         <v>28.100000381469727</v>
       </c>
       <c r="Q661" t="s">
-        <v>5565</v>
+        <v>5564</v>
       </c>
       <c r="R661" t="s">
         <v>56</v>
@@ -103741,7 +103762,7 @@
         <v>244</v>
       </c>
       <c r="T661" t="s">
-        <v>5566</v>
+        <v>5565</v>
       </c>
       <c r="U661" t="s">
         <v>102</v>
@@ -103762,7 +103783,7 @@
         <v>56</v>
       </c>
       <c r="AA661" t="s">
-        <v>5567</v>
+        <v>5566</v>
       </c>
       <c r="AB661" t="s">
         <v>56</v>
@@ -103795,7 +103816,7 @@
         <v>56</v>
       </c>
       <c r="AL661" t="s">
-        <v>5568</v>
+        <v>5567</v>
       </c>
       <c r="AM661" t="s">
         <v>56</v>
@@ -103860,13 +103881,13 @@
         <v>56</v>
       </c>
       <c r="J662" t="s">
-        <v>5593</v>
+        <v>5592</v>
       </c>
       <c r="K662" t="s">
         <v>5554</v>
       </c>
       <c r="L662" t="s">
-        <v>5569</v>
+        <v>5568</v>
       </c>
       <c r="M662">
         <v>-14.946045700000001</v>
@@ -103878,7 +103899,7 @@
         <v>400</v>
       </c>
       <c r="Q662" t="s">
-        <v>5570</v>
+        <v>5569</v>
       </c>
       <c r="R662" t="s">
         <v>56</v>
@@ -103887,7 +103908,7 @@
         <v>59</v>
       </c>
       <c r="T662" t="s">
-        <v>5571</v>
+        <v>5570</v>
       </c>
       <c r="U662" t="s">
         <v>61</v>
@@ -103908,7 +103929,7 @@
         <v>56</v>
       </c>
       <c r="AA662" t="s">
-        <v>5572</v>
+        <v>5571</v>
       </c>
       <c r="AB662" t="s">
         <v>56</v>
@@ -104006,13 +104027,13 @@
         <v>56</v>
       </c>
       <c r="J663" t="s">
-        <v>5594</v>
+        <v>5593</v>
       </c>
       <c r="K663" t="s">
-        <v>5557</v>
+        <v>5602</v>
       </c>
       <c r="L663" t="s">
-        <v>5573</v>
+        <v>5572</v>
       </c>
       <c r="M663">
         <v>-14.9814095</v>
@@ -104024,7 +104045,7 @@
         <v>3400</v>
       </c>
       <c r="Q663" t="s">
-        <v>5574</v>
+        <v>5573</v>
       </c>
       <c r="R663" t="s">
         <v>56</v>
@@ -104033,7 +104054,7 @@
         <v>79</v>
       </c>
       <c r="T663" t="s">
-        <v>5575</v>
+        <v>5574</v>
       </c>
       <c r="U663" t="s">
         <v>61</v>
@@ -104054,7 +104075,7 @@
         <v>56</v>
       </c>
       <c r="AA663" t="s">
-        <v>5576</v>
+        <v>5575</v>
       </c>
       <c r="AB663" t="s">
         <v>65</v>
@@ -104096,7 +104117,7 @@
         <v>135</v>
       </c>
       <c r="AO663" t="s">
-        <v>5577</v>
+        <v>5576</v>
       </c>
       <c r="AP663" t="s">
         <v>65</v>
@@ -104121,6 +104142,143 @@
       </c>
       <c r="AW663">
         <v>2099</v>
+      </c>
+    </row>
+    <row r="664" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="A664" t="s">
+        <v>5595</v>
+      </c>
+      <c r="B664" t="s">
+        <v>5596</v>
+      </c>
+      <c r="C664" t="s">
+        <v>52</v>
+      </c>
+      <c r="D664" t="s">
+        <v>53</v>
+      </c>
+      <c r="E664" t="s">
+        <v>4156</v>
+      </c>
+      <c r="F664" t="s">
+        <v>4156</v>
+      </c>
+      <c r="G664" t="s">
+        <v>759</v>
+      </c>
+      <c r="H664" t="s">
+        <v>5529</v>
+      </c>
+      <c r="I664" t="s">
+        <v>56</v>
+      </c>
+      <c r="J664" t="s">
+        <v>5598</v>
+      </c>
+      <c r="K664" t="s">
+        <v>5597</v>
+      </c>
+      <c r="L664" t="s">
+        <v>5599</v>
+      </c>
+      <c r="Q664" t="s">
+        <v>57</v>
+      </c>
+      <c r="R664" t="s">
+        <v>56</v>
+      </c>
+      <c r="S664" t="s">
+        <v>244</v>
+      </c>
+      <c r="T664" t="s">
+        <v>5600</v>
+      </c>
+      <c r="U664" t="s">
+        <v>61</v>
+      </c>
+      <c r="V664">
+        <v>2007</v>
+      </c>
+      <c r="W664">
+        <v>19</v>
+      </c>
+      <c r="X664" t="s">
+        <v>81</v>
+      </c>
+      <c r="Y664" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z664" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA664" t="s">
+        <v>971</v>
+      </c>
+      <c r="AB664" t="s">
+        <v>56</v>
+      </c>
+      <c r="AC664" t="s">
+        <v>56</v>
+      </c>
+      <c r="AD664" t="s">
+        <v>998</v>
+      </c>
+      <c r="AE664" t="s">
+        <v>56</v>
+      </c>
+      <c r="AF664" t="s">
+        <v>65</v>
+      </c>
+      <c r="AG664" t="s">
+        <v>56</v>
+      </c>
+      <c r="AH664" t="s">
+        <v>65</v>
+      </c>
+      <c r="AI664" t="s">
+        <v>65</v>
+      </c>
+      <c r="AJ664" t="s">
+        <v>5529</v>
+      </c>
+      <c r="AK664" t="s">
+        <v>5529</v>
+      </c>
+      <c r="AL664" t="s">
+        <v>5529</v>
+      </c>
+      <c r="AM664" t="s">
+        <v>56</v>
+      </c>
+      <c r="AN664" t="s">
+        <v>135</v>
+      </c>
+      <c r="AO664" t="s">
+        <v>5601</v>
+      </c>
+      <c r="AP664" t="s">
+        <v>65</v>
+      </c>
+      <c r="AQ664" t="s">
+        <v>5529</v>
+      </c>
+      <c r="AR664" t="s">
+        <v>5529</v>
+      </c>
+      <c r="AS664" t="s">
+        <v>85</v>
+      </c>
+      <c r="AT664">
+        <v>6.5926914599690079E-2</v>
+      </c>
+      <c r="AU664">
+        <v>0</v>
+      </c>
+      <c r="AV664" t="s">
+        <v>70</v>
+      </c>
+      <c r="AW664">
+        <v>2100</v>
       </c>
     </row>
   </sheetData>
